--- a/data/trans_orig/P1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Provincia-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,47 +723,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51164</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>47707</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51164</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -836,57 +836,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51164</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51164</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>47707</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>47707</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>47707</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51164</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51164</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -953,47 +953,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64934</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>67887</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64934</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1066,57 +1066,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64934</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64934</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>64934</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>67887</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>67887</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>67887</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>64934</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>64934</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>64934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1183,47 +1183,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67902</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>64697</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>67902</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,57 +1296,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67902</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67902</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67902</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>64697</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>64697</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>64697</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67902</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>67902</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,47 +1413,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>73516</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>66054</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>73516</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1526,57 +1526,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73516</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>73516</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73516</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66054</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>66054</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>66054</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>73516</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73516</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1643,47 +1643,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9541</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11399</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1756,57 +1756,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9541</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>9541</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>9541</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11399</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11399</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1873,47 +1873,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>52271</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>46659</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>52271</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1986,57 +1986,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>52271</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>52271</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>52271</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>46659</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>46659</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>46659</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>52271</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>52271</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>52271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2108,42 +2108,42 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>110786</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>110646</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>110786</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2221,52 +2221,52 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>110786</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>110786</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>110786</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>110646</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>110646</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>110646</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>110786</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>110786</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>110786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2333,47 +2333,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>96577</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>90167</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>96577</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2446,57 +2446,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>96577</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>96577</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>96577</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>90167</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>90167</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>90167</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>96577</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>96577</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>96577</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2563,47 +2563,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2676,57 +2676,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2861,7 +2861,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3029,47 +3029,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38080</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25357</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38080</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3142,57 +3142,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38080</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38080</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38080</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25357</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>25357</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>25357</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38080</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38080</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>38080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3259,47 +3259,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>58886</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>54386</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>58886</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3372,57 +3372,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58886</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>58886</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>58886</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54386</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>54386</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>54386</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>58886</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>58886</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>58886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3489,47 +3489,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59934</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>52713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>59934</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3602,57 +3602,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>59934</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>59934</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>59934</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>52713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>52713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>52713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>59934</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>59934</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>59934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3719,47 +3719,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55472</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>49680</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>55472</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3832,57 +3832,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55472</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>55472</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55472</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>49680</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>49680</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>49680</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>55472</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>55472</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>55472</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3949,47 +3949,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24630</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18043</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -4062,57 +4062,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24630</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24630</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24630</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18043</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>18043</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>18043</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4179,47 +4179,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49533</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>44542</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4292,57 +4292,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49533</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49533</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49533</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>44542</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>44542</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>44542</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4409,47 +4409,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>121777</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>116704</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>121777</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>121777</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>121777</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121777</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>116704</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>116704</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>116704</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>121777</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>121777</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>121777</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4639,47 +4639,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>130468</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>115539</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>130468</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4752,57 +4752,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>130468</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>130468</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>130468</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>115539</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>115539</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>115539</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>130468</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>130468</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>130468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4869,47 +4869,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4982,57 +4982,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5167,7 +5167,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5335,47 +5335,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51994</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>45386</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51994</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5448,57 +5448,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51994</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51994</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51994</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>45386</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>45386</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>45386</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51994</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51994</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5565,47 +5565,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>79995</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70702</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>79995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -5678,57 +5678,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>79995</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>79995</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>79995</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>70702</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>70702</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>70702</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>79995</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>79995</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>79995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5795,47 +5795,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66177</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>58113</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>66177</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5908,57 +5908,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>66177</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>66177</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>66177</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>58113</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>58113</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>58113</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>66177</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>66177</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>66177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6030,42 +6030,42 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>47650</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>45113</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -6143,52 +6143,52 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>47650</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47650</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>47650</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>45113</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>45113</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>45113</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6255,47 +6255,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35516</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32375</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35516</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -6368,57 +6368,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35516</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35516</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35516</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>32375</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>32375</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>32375</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35516</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>35516</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>35516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6485,47 +6485,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>27283</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>31356</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -6598,57 +6598,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>27283</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>27283</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>27283</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>31356</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>31356</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>31356</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6715,47 +6715,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>119123</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>116765</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>119123</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -6828,57 +6828,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>119123</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>119123</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>119123</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>116765</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>116765</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>116765</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>119123</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>119123</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>119123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6945,47 +6945,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139223</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>129653</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139223</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -7058,57 +7058,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>139223</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>139223</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>139223</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>129653</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>129653</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>129653</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>139223</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>139223</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>139223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7175,47 +7175,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7288,57 +7288,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7473,7 +7473,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7641,47 +7641,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -7754,57 +7754,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7829,17 +7829,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7871,47 +7871,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -7984,57 +7984,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8101,47 +8101,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -8214,57 +8214,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8289,17 +8289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8331,47 +8331,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -8444,57 +8444,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8519,17 +8519,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8561,47 +8561,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -8674,57 +8674,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8749,17 +8749,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8791,47 +8791,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -8904,57 +8904,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8979,17 +8979,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9021,47 +9021,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -9134,57 +9134,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9209,17 +9209,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9251,47 +9251,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -9364,57 +9364,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9439,17 +9439,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9481,47 +9481,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -9594,57 +9594,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9669,17 +9669,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
